--- a/Assets/StreamingAssets/story/1.xlsx
+++ b/Assets/StreamingAssets/story/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\23272\Desktop\unity\jiachi\Assets\StreamingAssets\story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B65FE36-2D86-4A3B-85EF-754628733770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE63AD8-E36E-4B4E-9BC1-02DD8049F869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1410" yWindow="1500" windowWidth="20000" windowHeight="13190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4710" yWindow="7970" windowWidth="20000" windowHeight="7260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,13 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="54">
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Dialogue</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
   <si>
     <t>Avatar</t>
   </si>
@@ -58,18 +52,6 @@
     <t>Character2</t>
   </si>
   <si>
-    <t>LastBGlmg</t>
-  </si>
-  <si>
-    <t>LastBGM</t>
-  </si>
-  <si>
-    <t>LastX1</t>
-  </si>
-  <si>
-    <t>LastX2</t>
-  </si>
-  <si>
     <t>English Name</t>
   </si>
   <si>
@@ -166,22 +148,43 @@
     <t>choice</t>
   </si>
   <si>
-    <t>你好来2</t>
-  </si>
-  <si>
-    <t>choice2</t>
-  </si>
-  <si>
-    <t>Route 2</t>
-  </si>
-  <si>
-    <t>ルート2</t>
-  </si>
-  <si>
     <t>[Name]</t>
   </si>
   <si>
     <t>[Name]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文名字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选1
+选2
+选3
+选4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-1-1
+1-1-2
+1-1-3
+1-1-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A1
+B2
+C3
+D4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>良治</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -225,8 +228,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -507,96 +516,83 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.25" customWidth="1"/>
-    <col min="3" max="4" width="0" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="6.1640625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="5.58203125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="6.6640625" hidden="1" customWidth="1"/>
-    <col min="9" max="11" width="0" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="9.58203125" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5" hidden="1" customWidth="1"/>
-    <col min="14" max="16" width="0" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="11.75" customWidth="1"/>
-    <col min="18" max="18" width="27.75" customWidth="1"/>
-    <col min="19" max="19" width="12.75" customWidth="1"/>
-    <col min="20" max="20" width="24.75" customWidth="1"/>
+    <col min="3" max="4" width="8.6640625" customWidth="1"/>
+    <col min="5" max="5" width="6.1640625" customWidth="1"/>
+    <col min="6" max="6" width="5.58203125" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" customWidth="1"/>
+    <col min="9" max="10" width="8.6640625" customWidth="1"/>
+    <col min="11" max="11" width="4.1640625" customWidth="1"/>
+    <col min="12" max="12" width="9.58203125" customWidth="1"/>
+    <col min="13" max="13" width="11.75" customWidth="1"/>
+    <col min="14" max="14" width="27.75" customWidth="1"/>
+    <col min="15" max="15" width="12.75" customWidth="1"/>
+    <col min="16" max="16" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -605,321 +601,215 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H2">
         <v>-500</v>
       </c>
       <c r="I2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
         <v>20</v>
       </c>
-      <c r="Q2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R2" t="s">
-        <v>23</v>
-      </c>
-      <c r="S2" t="s">
-        <v>52</v>
-      </c>
-      <c r="T2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H3">
         <v>-400</v>
       </c>
       <c r="J3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K3">
         <v>800</v>
       </c>
       <c r="L3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P3" t="s">
         <v>25</v>
       </c>
-      <c r="M3">
-        <f t="shared" ref="M3:N8" si="0">IF(E2&lt;&gt;"",E2,M2)</f>
-        <v>3</v>
-      </c>
-      <c r="N3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O3">
-        <f t="shared" ref="O3:O8" si="1">IF(H2&lt;&gt;"",H2,O2)</f>
-        <v>-500</v>
-      </c>
-      <c r="P3">
-        <f t="shared" ref="P3:P8" si="2">IF(K2&lt;&gt;"",K2,P2)</f>
-        <v>0</v>
-      </c>
-      <c r="Q3" t="s">
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" t="s">
+        <v>42</v>
+      </c>
+      <c r="P4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
         <v>28</v>
       </c>
-      <c r="R3" t="s">
-        <v>29</v>
-      </c>
-      <c r="S3" t="s">
-        <v>30</v>
-      </c>
-      <c r="T3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="N4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <f t="shared" si="1"/>
-        <v>-400</v>
-      </c>
-      <c r="P4">
-        <f t="shared" si="2"/>
-        <v>800</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>52</v>
-      </c>
-      <c r="R4" t="s">
-        <v>33</v>
-      </c>
-      <c r="S4" t="s">
-        <v>52</v>
-      </c>
-      <c r="T4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K5">
         <v>700</v>
       </c>
-      <c r="M5">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="N5">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <f t="shared" si="1"/>
-        <v>-400</v>
-      </c>
-      <c r="P5">
-        <f t="shared" si="2"/>
-        <v>800</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>28</v>
-      </c>
-      <c r="R5" t="s">
+      <c r="M5" t="s">
+        <v>22</v>
+      </c>
+      <c r="N5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" t="s">
+        <v>24</v>
+      </c>
+      <c r="P5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" t="s">
+        <v>42</v>
+      </c>
+      <c r="N6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O6" t="s">
+        <v>42</v>
+      </c>
+      <c r="P6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" t="s">
         <v>35</v>
-      </c>
-      <c r="S5" t="s">
-        <v>30</v>
-      </c>
-      <c r="T5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="N6">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O6">
-        <f t="shared" si="1"/>
-        <v>-400</v>
-      </c>
-      <c r="P6">
-        <f t="shared" si="2"/>
-        <v>700</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>52</v>
-      </c>
-      <c r="R6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S6" t="s">
-        <v>52</v>
-      </c>
-      <c r="T6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" t="s">
-        <v>41</v>
       </c>
       <c r="K7">
         <v>800</v>
       </c>
-      <c r="M7">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="N7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <f t="shared" si="1"/>
-        <v>-400</v>
-      </c>
-      <c r="P7">
-        <f t="shared" si="2"/>
-        <v>700</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>28</v>
-      </c>
-      <c r="R7" t="s">
-        <v>42</v>
-      </c>
-      <c r="S7" t="s">
-        <v>30</v>
-      </c>
-      <c r="T7" t="s">
-        <v>43</v>
+      <c r="M7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P7" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H8">
         <v>-500</v>
       </c>
-      <c r="M8">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="N8">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <f t="shared" si="1"/>
-        <v>-400</v>
-      </c>
-      <c r="P8">
-        <f t="shared" si="2"/>
-        <v>800</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>52</v>
-      </c>
-      <c r="R8" t="s">
-        <v>45</v>
-      </c>
-      <c r="S8" t="s">
-        <v>52</v>
-      </c>
-      <c r="T8" t="s">
+      <c r="M8" t="s">
+        <v>42</v>
+      </c>
+      <c r="N8" t="s">
+        <v>39</v>
+      </c>
+      <c r="O8" t="s">
+        <v>42</v>
+      </c>
+      <c r="P8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="56" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="C9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B9" t="s">
+      <c r="M9" s="2"/>
+      <c r="N9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9">
-        <v>3</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>47</v>
-      </c>
-      <c r="R9" t="s">
-        <v>50</v>
-      </c>
-      <c r="S9" t="s">
-        <v>47</v>
-      </c>
-      <c r="T9" t="s">
-        <v>51</v>
+      <c r="O9" s="2"/>
+      <c r="P9" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/story/1.xlsx
+++ b/Assets/StreamingAssets/story/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\23272\Desktop\unity\jiachi\Assets\StreamingAssets\story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE63AD8-E36E-4B4E-9BC1-02DD8049F869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE2B247-12E7-4FB0-9982-27974CA0407A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4710" yWindow="7970" windowWidth="20000" windowHeight="7260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7410" yWindow="810" windowWidth="12590" windowHeight="14470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="80">
   <si>
     <t>Avatar</t>
   </si>
@@ -34,24 +34,6 @@
     <t>Bgm</t>
   </si>
   <si>
-    <t>Action1</t>
-  </si>
-  <si>
-    <t>x1</t>
-  </si>
-  <si>
-    <t>Character1</t>
-  </si>
-  <si>
-    <t>Action2</t>
-  </si>
-  <si>
-    <t>x2</t>
-  </si>
-  <si>
-    <t>Character2</t>
-  </si>
-  <si>
     <t>English Name</t>
   </si>
   <si>
@@ -67,27 +49,12 @@
     <t>良治</t>
   </si>
   <si>
-    <t>额…おはよう</t>
-  </si>
-  <si>
-    <t>appearAt</t>
-  </si>
-  <si>
     <t>Uh... Good morning.</t>
   </si>
   <si>
     <t>えっと…おはよう。</t>
   </si>
   <si>
-    <t>樱</t>
-  </si>
-  <si>
-    <t>好久不见。</t>
-  </si>
-  <si>
-    <t>moveTo</t>
-  </si>
-  <si>
     <t>Sakura</t>
   </si>
   <si>
@@ -106,39 +73,24 @@
     <t>It's been a while.</t>
   </si>
   <si>
-    <t>你怎么还和以前一样。</t>
-  </si>
-  <si>
     <t>You're still the same as before.</t>
   </si>
   <si>
     <t>相変わらずだね。</t>
   </si>
   <si>
-    <t>怎么了。</t>
-  </si>
-  <si>
     <t>What's wrong?</t>
   </si>
   <si>
     <t>どうしたの？</t>
   </si>
   <si>
-    <t>没事，我先走了。</t>
-  </si>
-  <si>
-    <t>disappear</t>
-  </si>
-  <si>
     <t>It's nothing. I'll get going first.</t>
   </si>
   <si>
     <t>なんでもない。先に行くね。</t>
   </si>
   <si>
-    <t>再见了。</t>
-  </si>
-  <si>
     <t>Goodbye.</t>
   </si>
   <si>
@@ -151,29 +103,7 @@
     <t>[Name]</t>
   </si>
   <si>
-    <t>[Name]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>中文名字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中文对话</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选1
-选2
-选3
-选4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1-1-1
-1-1-2
-1-1-3
-1-1-4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -185,6 +115,222 @@
   </si>
   <si>
     <t>良治</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Name]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>声音和记忆里一样。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可我却一瞬间明白——</t>
+  </si>
+  <si>
+    <t>那个曾经只属于我的称呼，已经不再属于我了。</t>
+  </si>
+  <si>
+    <t>很久以来，一切都未曾改变。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沐浴着和煦的阳光，伴随着四季的悄然轮回。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从未怀疑过什么，平凡的日子就这样度过....</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这一切，你几乎感觉不到，因为，它是那样的从容.....</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我已深深地感觉到......冬天，来了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>忽然间才发现......在不经意的时候，秋天已悄然而去....</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「[Name]。」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「啊.....好久不见。」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「放心吧。」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「我会好好完成小组任务的。」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「以前的事，我不会带进来。」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「……嗯。那就好。」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>那就好。</t>
+  </si>
+  <si>
+    <t>我明明应该这么想。</t>
+  </si>
+  <si>
+    <t>可是胸口却像被什么轻轻划开了。</t>
+  </si>
+  <si>
+    <t>马上就是圣诞节了，不知道这次文化祭的小组成员好不好相处呢。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我趴在桌子上放空大脑。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>突然，一声熟悉的声音把我拉回现实。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>她叫我的名字。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「这次我们文化祭展示，两人先一组。」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文对话「」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们像两个第一次见面的人一样低头。</t>
+  </si>
+  <si>
+    <t>熟练，礼貌，陌生。</t>
+  </si>
+  <si>
+    <t>真恶心。</t>
+  </si>
+  <si>
+    <t>「请多指教。」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>......</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「以上就是我们的大概规划，老师非常相信你们，有需要帮助的就和我说好了。」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「现在解散。」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>呼——总算结束了。其实我对这活动没什么期待的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只是…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在干嘛好呢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>和樱讨论下策划案
+先一个人去走廊冷静一下	
+回家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跳转文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好感度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好感度条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterCommands</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">laoshi
+disappear
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kaji
+appearAt
+0
+normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sakura
+appearAt
+0.6
+normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laoshi
+appearAt
+0.4
+normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">sakura
+disappear;
+kaji
+disappear;
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1
+2.2
+2.3
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sakura:+50;yuzuki:-25
+sakura:-50;yuzuki:+50
+sakura:-100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">sakura:0,100
+sakura:0,0
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -192,7 +338,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -206,6 +352,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -228,13 +381,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -516,30 +676,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.25" customWidth="1"/>
-    <col min="3" max="4" width="8.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.1640625" customWidth="1"/>
-    <col min="6" max="6" width="5.58203125" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" customWidth="1"/>
-    <col min="8" max="8" width="6.6640625" customWidth="1"/>
-    <col min="9" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="4.1640625" customWidth="1"/>
-    <col min="12" max="12" width="9.58203125" customWidth="1"/>
-    <col min="13" max="13" width="11.75" customWidth="1"/>
-    <col min="14" max="14" width="27.75" customWidth="1"/>
-    <col min="15" max="15" width="12.75" customWidth="1"/>
-    <col min="16" max="16" width="24.75" customWidth="1"/>
+    <col min="2" max="2" width="39.5" customWidth="1"/>
+    <col min="3" max="3" width="7.75" customWidth="1"/>
+    <col min="4" max="4" width="19.25" customWidth="1"/>
+    <col min="5" max="5" width="11.4140625" customWidth="1"/>
+    <col min="6" max="6" width="4.5" customWidth="1"/>
+    <col min="7" max="7" width="21.4140625" customWidth="1"/>
+    <col min="8" max="8" width="11.75" customWidth="1"/>
+    <col min="9" max="9" width="27.75" customWidth="1"/>
+    <col min="10" max="10" width="12.75" customWidth="1"/>
+    <col min="11" max="11" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -554,266 +711,386 @@
         <v>3</v>
       </c>
       <c r="G1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="56" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" t="s">
+        <v>13</v>
+      </c>
+      <c r="K12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" t="s">
+        <v>13</v>
+      </c>
+      <c r="K16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="58.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="17.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J18" s="2"/>
+      <c r="K18" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" t="s">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="56" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2">
-        <v>-500</v>
-      </c>
-      <c r="I2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" t="s">
-        <v>17</v>
-      </c>
-      <c r="O2" t="s">
-        <v>42</v>
-      </c>
-      <c r="P2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3">
-        <v>-400</v>
-      </c>
-      <c r="J3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3">
-        <v>800</v>
-      </c>
-      <c r="L3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O3" t="s">
-        <v>24</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="B25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="70" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="42" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" t="s">
+        <v>61</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C36" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" t="s">
+        <v>67</v>
+      </c>
+      <c r="E36" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="56" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="M4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" t="s">
-        <v>42</v>
-      </c>
-      <c r="P4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5">
-        <v>700</v>
-      </c>
-      <c r="M5" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O5" t="s">
-        <v>24</v>
-      </c>
-      <c r="P5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="M6" t="s">
-        <v>42</v>
-      </c>
-      <c r="N6" t="s">
-        <v>32</v>
-      </c>
-      <c r="O6" t="s">
-        <v>42</v>
-      </c>
-      <c r="P6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7">
-        <v>800</v>
-      </c>
-      <c r="M7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N7" t="s">
-        <v>36</v>
-      </c>
-      <c r="O7" t="s">
-        <v>24</v>
-      </c>
-      <c r="P7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8">
-        <v>-500</v>
-      </c>
-      <c r="M8" t="s">
-        <v>42</v>
-      </c>
-      <c r="N8" t="s">
-        <v>39</v>
-      </c>
-      <c r="O8" t="s">
-        <v>42</v>
-      </c>
-      <c r="P8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="56" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="1" t="s">
-        <v>48</v>
+      <c r="B37" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/story/1.xlsx
+++ b/Assets/StreamingAssets/story/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\23272\Desktop\unity\jiachi\Assets\StreamingAssets\story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE2B247-12E7-4FB0-9982-27974CA0407A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391443BA-0D99-4640-80C8-901EF7A98CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7410" yWindow="810" windowWidth="12590" windowHeight="14470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9730" yWindow="810" windowWidth="13280" windowHeight="14470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="86">
   <si>
     <t>Avatar</t>
   </si>
@@ -276,61 +276,99 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>先生</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">laoshi
 disappear
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>kaji
-appearAt
-0
-normal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sakura
-appearAt
-0.6
-normal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>laoshi
-appearAt
-0.4
-normal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">sakura
-disappear;
-kaji
-disappear;
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1
-2.2
-2.3
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>sakura:+50;yuzuki:-25
 sakura:-50;yuzuki:+50
 sakura:-100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">sakura:0,100
-sakura:0,0
+    <t>yuzuki
+appearAtWithL2d
+500
+idle
+800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yuzuki
+moveTo
+-500
+idle
+800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yuzuki
+moveTo
+500
+idle
+800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yuzuki
+disappear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2-1
+2-2
+2-3
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1线50，2线-50，三线-100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sakura:0,100
+sakura:0,100
+sakura:0,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kaji
+appearAt
+300
+1
+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sakura
+appearAt
+1300
+1
+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kaji
+disappear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sakura
+disappear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>laoshi
+appearAt
+800
+1
+1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -681,9 +719,9 @@
   <cols>
     <col min="2" max="2" width="39.5" customWidth="1"/>
     <col min="3" max="3" width="7.75" customWidth="1"/>
-    <col min="4" max="4" width="19.25" customWidth="1"/>
-    <col min="5" max="5" width="11.4140625" customWidth="1"/>
-    <col min="6" max="6" width="4.5" customWidth="1"/>
+    <col min="4" max="4" width="6.5" customWidth="1"/>
+    <col min="5" max="5" width="6" customWidth="1"/>
+    <col min="6" max="6" width="4.83203125" customWidth="1"/>
     <col min="7" max="7" width="21.4140625" customWidth="1"/>
     <col min="8" max="8" width="11.75" customWidth="1"/>
     <col min="9" max="9" width="27.75" customWidth="1"/>
@@ -726,27 +764,39 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="70" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>34</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G2" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="70" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G3" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="70" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G4" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>37</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -791,7 +841,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="56" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="70" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -802,7 +852,7 @@
         <v>29</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s">
         <v>11</v>
@@ -817,9 +867,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>52</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="H13" t="s">
         <v>26</v>
@@ -885,7 +938,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="58.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:11" ht="72.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -896,7 +949,7 @@
         <v>70</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s">
         <v>26</v>
@@ -940,8 +993,9 @@
       <c r="C19" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="1:11" ht="28" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -950,6 +1004,9 @@
       </c>
       <c r="C20" t="s">
         <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -970,15 +1027,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="56" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="70" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="B24" t="s">
         <v>53</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
@@ -1003,13 +1060,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="70" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>55</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>76</v>
-      </c>
+      <c r="G27" s="3"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
@@ -1028,7 +1083,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="B31" t="s">
         <v>60</v>
@@ -1036,31 +1091,31 @@
     </row>
     <row r="32" spans="1:11" ht="42" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="B32" t="s">
         <v>61</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
         <v>66</v>
       </c>
@@ -1070,8 +1125,11 @@
       <c r="E36" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" ht="56" x14ac:dyDescent="0.3">
+      <c r="F36" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="140" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -1082,7 +1140,7 @@
         <v>77</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>79</v>

--- a/Assets/StreamingAssets/story/1.xlsx
+++ b/Assets/StreamingAssets/story/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\23272\Desktop\unity\jiachi\Assets\StreamingAssets\story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391443BA-0D99-4640-80C8-901EF7A98CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B8964A-62FD-4ED5-A6E5-F7FDB21BC601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9730" yWindow="810" windowWidth="13280" windowHeight="14470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="90">
   <si>
     <t>Avatar</t>
   </si>
@@ -247,12 +247,6 @@
   </si>
   <si>
     <t>现在干嘛好呢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>和樱讨论下策划案
-先一个人去走廊冷静一下	
-回家</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -369,6 +363,28 @@
 800
 1
 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回家吧看看妹妹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>game</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MuScene</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>还是被桜的电话叫回学校了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>和桜讨论下策划案
+先一个人去走廊冷静一下	
+回家</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -714,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="39.5" customWidth="1"/>
@@ -749,7 +765,7 @@
         <v>3</v>
       </c>
       <c r="G1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H1" t="s">
         <v>4</v>
@@ -772,7 +788,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="70" x14ac:dyDescent="0.3">
@@ -780,7 +796,7 @@
         <v>35</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="70" x14ac:dyDescent="0.3">
@@ -788,7 +804,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="28" x14ac:dyDescent="0.3">
@@ -796,7 +812,7 @@
         <v>37</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -852,7 +868,7 @@
         <v>29</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s">
         <v>11</v>
@@ -872,7 +888,7 @@
         <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s">
         <v>26</v>
@@ -946,10 +962,10 @@
         <v>42</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H17" t="s">
         <v>26</v>
@@ -1006,7 +1022,7 @@
         <v>8</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -1029,18 +1045,18 @@
     </row>
     <row r="24" spans="1:11" ht="70" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B24" t="s">
         <v>53</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="B25" t="s">
         <v>58</v>
@@ -1083,7 +1099,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B31" t="s">
         <v>60</v>
@@ -1091,13 +1107,13 @@
     </row>
     <row r="32" spans="1:11" ht="42" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B32" t="s">
         <v>61</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -1116,34 +1132,58 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C36" t="s">
+      <c r="B36" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C39" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" t="s">
         <v>66</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E39" t="s">
         <v>67</v>
       </c>
-      <c r="E36" t="s">
-        <v>68</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="F39" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="140" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E40" s="5" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="140" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>25</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/story/1.xlsx
+++ b/Assets/StreamingAssets/story/1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\23272\Desktop\unity\jiachi\Assets\StreamingAssets\story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B8964A-62FD-4ED5-A6E5-F7FDB21BC601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3C6496-1166-4BB5-99C8-138BCF76B089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9730" yWindow="810" windowWidth="13280" windowHeight="14470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="91">
   <si>
     <t>Avatar</t>
   </si>
@@ -385,6 +385,10 @@
     <t>和桜讨论下策划案
 先一个人去走廊冷静一下	
 回家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>End of story</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -730,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="39.5" customWidth="1"/>
@@ -1132,57 +1136,62 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B36" t="s">
+      <c r="A36" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
         <v>85</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>86</v>
-      </c>
-      <c r="B37" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>30</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>88</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C39" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C39" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C40" t="s">
         <v>65</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D40" t="s">
         <v>66</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E40" t="s">
         <v>67</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F40" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="140" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="41" spans="1:6" ht="140" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>25</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B41" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C41" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D41" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E41" s="5" t="s">
         <v>78</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/story/1.xlsx
+++ b/Assets/StreamingAssets/story/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\23272\Desktop\unity\jiachi\Assets\StreamingAssets\story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3C6496-1166-4BB5-99C8-138BCF76B089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF52A4B-B237-4D49-9367-F6BF02C30C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Assets/StreamingAssets/story/1.xlsx
+++ b/Assets/StreamingAssets/story/1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\23272\Desktop\unity\jiachi\Assets\StreamingAssets\story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF52A4B-B237-4D49-9367-F6BF02C30C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8602A075-516A-4ECE-B4C5-982AB32D92FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12230" yWindow="490" windowWidth="13280" windowHeight="14470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="93">
   <si>
     <t>Avatar</t>
   </si>
@@ -389,6 +389,14 @@
   </si>
   <si>
     <t>End of story</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quest_unlock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visit_school_once</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -734,7 +742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="39.5" customWidth="1"/>
@@ -795,403 +803,412 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="70" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="62.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>91</v>
+      </c>
       <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>73</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:11" ht="70" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="70" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
         <v>36</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="28" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
+    <row r="6" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>49</v>
+        <v>38</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="70" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="13" spans="1:11" ht="70" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>30</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>41</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H13" t="s">
         <v>11</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I13" t="s">
         <v>12</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J13" t="s">
         <v>13</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="28" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
+    <row r="14" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H14" t="s">
         <v>26</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I14" t="s">
         <v>16</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J14" t="s">
         <v>26</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K14" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" t="s">
-        <v>13</v>
-      </c>
-      <c r="K14" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H15" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J15" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="K15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" t="s">
+        <v>26</v>
+      </c>
+      <c r="K16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
         <v>33</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H17" t="s">
         <v>11</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I17" t="s">
         <v>21</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J17" t="s">
         <v>13</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K17" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="72.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I17" t="s">
-        <v>23</v>
-      </c>
-      <c r="J17" t="s">
-        <v>26</v>
-      </c>
-      <c r="K17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="17.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="72.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J18" s="2"/>
-      <c r="K18" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="17.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
-      <c r="B19" t="s">
-        <v>44</v>
+      <c r="B19" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="C19" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+      <c r="H19" s="2"/>
+      <c r="I19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="2"/>
+      <c r="K19" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="1:11" ht="28" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>30</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
         <v>45</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C21" t="s">
         <v>8</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
         <v>48</v>
       </c>
-      <c r="E23">
+      <c r="E24">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="70" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="25" spans="1:11" ht="70" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>82</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" t="s">
         <v>53</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G25" s="3" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="B26" t="s">
         <v>58</v>
       </c>
       <c r="C26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>55</v>
-      </c>
-      <c r="G27" s="3"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>56</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G28" s="3"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>82</v>
-      </c>
-      <c r="B31" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="42" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>82</v>
       </c>
       <c r="B32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="42" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" t="s">
         <v>61</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G33" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B33" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B34" t="s">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B35" t="s">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B37" t="s">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>86</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>30</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>88</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C40" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C41" t="s">
         <v>65</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D41" t="s">
         <v>66</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E41" t="s">
         <v>67</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F41" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="140" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="42" spans="1:7" ht="140" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B42" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C42" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D42" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E42" s="5" t="s">
         <v>78</v>
       </c>
     </row>
